--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1025_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1025_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Dont Look</t>
         </is>
       </c>
@@ -477,6 +482,9 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3428965508937836</v>
       </c>
     </row>
@@ -497,6 +505,9 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.2176737785339355</v>
       </c>
     </row>
@@ -517,6 +528,9 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.3836647868156433</v>
       </c>
     </row>
@@ -537,6 +551,9 @@
         <v>0.4385379552841187</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.2794946730136871</v>
       </c>
     </row>
@@ -557,6 +574,9 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.2192490100860596</v>
       </c>
     </row>
@@ -577,6 +597,9 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.3764612376689911</v>
       </c>
     </row>
@@ -597,6 +620,9 @@
         <v>0.4093373417854309</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.4144656658172607</v>
       </c>
     </row>
@@ -619,6 +645,9 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -639,6 +668,9 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -659,6 +691,9 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -679,6 +714,9 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -699,6 +737,9 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -719,6 +760,9 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -737,6 +781,9 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.5163909196853638</v>
       </c>
     </row>
@@ -757,6 +804,9 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.4022208750247955</v>
       </c>
     </row>
@@ -777,6 +827,9 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.4003255665302277</v>
       </c>
     </row>
@@ -797,6 +850,9 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.2809014618396759</v>
       </c>
     </row>
@@ -816,7 +872,8 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -836,7 +893,8 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -856,7 +914,8 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0.4625914692878723</v>
       </c>
     </row>
@@ -874,7 +933,8 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>-0.01159773394465446</v>
       </c>
     </row>
@@ -892,7 +952,8 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -910,7 +971,8 @@
       <c r="E24" t="n">
         <v>0.6072185039520264</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,7 +988,8 @@
       <c r="E25" t="n">
         <v>0.6486700177192688</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.4345588684082031</v>
       </c>
     </row>
@@ -942,7 +1005,8 @@
       <c r="E26" t="n">
         <v>0.5510326623916626</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.4378305971622467</v>
       </c>
     </row>
@@ -958,7 +1022,8 @@
       <c r="E27" t="n">
         <v>0.4822142124176025</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.3926019370555878</v>
       </c>
     </row>
@@ -974,7 +1039,8 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -990,7 +1056,8 @@
       <c r="E29" t="n">
         <v>0.4546554386615753</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0.4203191995620728</v>
       </c>
     </row>
@@ -1006,7 +1073,8 @@
       <c r="E30" t="n">
         <v>0.401833564043045</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,7 +1088,8 @@
         <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,7 +1103,8 @@
         <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,7 +1118,8 @@
         <v>0.3536044359207153</v>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.7529618740081787</v>
       </c>
     </row>
@@ -1062,7 +1133,8 @@
         <v>0</v>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.2360927909612656</v>
       </c>
     </row>
@@ -1076,7 +1148,8 @@
         <v>0.1641936600208282</v>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.7606840133666992</v>
       </c>
     </row>
@@ -1090,7 +1163,8 @@
         <v>0</v>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.4629412293434143</v>
       </c>
     </row>
@@ -1104,7 +1178,8 @@
         <v>0.4132596254348755</v>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0.540124773979187</v>
       </c>
     </row>
@@ -1118,7 +1193,8 @@
         <v>0.4667340517044067</v>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1132,7 +1208,8 @@
         <v>0.1704845875501633</v>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0.4823108911514282</v>
       </c>
     </row>
@@ -1146,7 +1223,8 @@
         <v>0</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0.4010852575302124</v>
       </c>
     </row>
@@ -1160,7 +1238,8 @@
         <v>0.1367611140012741</v>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1174,7 +1253,8 @@
         <v>0.2164732366800308</v>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.5524951815605164</v>
       </c>
     </row>
@@ -1189,6 +1269,7 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1201,6 +1282,7 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1213,6 +1295,7 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1225,6 +1308,7 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1237,6 +1321,7 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1249,6 +1334,7 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1261,6 +1347,7 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1273,6 +1360,7 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1285,6 +1373,7 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1297,6 +1386,7 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1309,6 +1399,7 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1321,6 +1412,7 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1333,6 +1425,7 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1345,6 +1438,7 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
